--- a/docs/TECH_EARNEST_CRM_SPRINT_BACKLOG_WORKING.xlsx
+++ b/docs/TECH_EARNEST_CRM_SPRINT_BACKLOG_WORKING.xlsx
@@ -3552,7 +3552,7 @@
         <v>8</v>
       </c>
       <c r="L50" t="str">
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="M50" t="str">
         <v/>
@@ -3561,10 +3561,10 @@
         <v>US-S8-003</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>Verified implemented per batch 10</v>
       </c>
     </row>
     <row r="51">
@@ -3602,7 +3602,7 @@
         <v>5</v>
       </c>
       <c r="L51" t="str">
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="M51" t="str">
         <v/>
@@ -3611,10 +3611,10 @@
         <v>US-S8-001</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P51" t="str">
-        <v/>
+        <v>Verified implemented per batch 10</v>
       </c>
     </row>
     <row r="52">
@@ -3652,7 +3652,7 @@
         <v>13</v>
       </c>
       <c r="L52" t="str">
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="M52" t="str">
         <v/>
@@ -3661,10 +3661,10 @@
         <v>US-S8-003</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P52" t="str">
-        <v/>
+        <v>Verified implemented per batch 10</v>
       </c>
     </row>
     <row r="53">
@@ -3702,7 +3702,7 @@
         <v>13</v>
       </c>
       <c r="L53" t="str">
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="M53" t="str">
         <v/>
@@ -3711,10 +3711,10 @@
         <v>US-S9-001,US-S4-006</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P53" t="str">
-        <v/>
+        <v>Verified implemented per batch 10</v>
       </c>
     </row>
     <row r="54">
@@ -3752,7 +3752,7 @@
         <v>13</v>
       </c>
       <c r="L54" t="str">
-        <v>In Progress</v>
+        <v>Done</v>
       </c>
       <c r="M54" t="str">
         <v/>
@@ -3761,10 +3761,10 @@
         <v>US-S8-002</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P54" t="str">
-        <v/>
+        <v>Verified implemented per batch 10</v>
       </c>
     </row>
     <row r="55">
@@ -5802,7 +5802,7 @@
         <v>13</v>
       </c>
       <c r="L95" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M95" t="str">
         <v/>
@@ -5811,10 +5811,10 @@
         <v/>
       </c>
       <c r="O95" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P95" t="str">
-        <v/>
+        <v>Routes/nav wired; expense UI aligned; Approval Engine integrated</v>
       </c>
     </row>
     <row r="96">
@@ -5852,7 +5852,7 @@
         <v>8</v>
       </c>
       <c r="L96" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M96" t="str">
         <v/>
@@ -5861,10 +5861,10 @@
         <v>US-S14-001,US-S20-001</v>
       </c>
       <c r="O96" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P96" t="str">
-        <v/>
+        <v>Routes/nav wired; expense UI aligned; Approval Engine integrated</v>
       </c>
     </row>
     <row r="97">
@@ -5902,7 +5902,7 @@
         <v>5</v>
       </c>
       <c r="L97" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M97" t="str">
         <v/>
@@ -5911,10 +5911,10 @@
         <v/>
       </c>
       <c r="O97" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P97" t="str">
-        <v/>
+        <v>Routes/nav wired; expense UI aligned; Approval Engine integrated</v>
       </c>
     </row>
     <row r="98">
@@ -5952,7 +5952,7 @@
         <v>8</v>
       </c>
       <c r="L98" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M98" t="str">
         <v/>
@@ -5961,10 +5961,10 @@
         <v/>
       </c>
       <c r="O98" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P98" t="str">
-        <v/>
+        <v>Routes/nav wired; expense UI aligned; Approval Engine integrated</v>
       </c>
     </row>
     <row r="99">
@@ -6002,7 +6002,7 @@
         <v>13</v>
       </c>
       <c r="L99" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M99" t="str">
         <v/>
@@ -6011,10 +6011,10 @@
         <v>US-S21-001</v>
       </c>
       <c r="O99" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P99" t="str">
-        <v/>
+        <v>Routes/nav wired; expense UI aligned; Approval Engine integrated</v>
       </c>
     </row>
     <row r="100">
@@ -6052,7 +6052,7 @@
         <v>13</v>
       </c>
       <c r="L100" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M100" t="str">
         <v/>
@@ -6061,10 +6061,10 @@
         <v>US-S14-001,US-S21-002</v>
       </c>
       <c r="O100" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P100" t="str">
-        <v/>
+        <v>PO lifecycle+Approval; reports API+UI; vendor/PO query APIs</v>
       </c>
     </row>
     <row r="101">
@@ -6102,7 +6102,7 @@
         <v>5</v>
       </c>
       <c r="L101" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M101" t="str">
         <v/>
@@ -6111,10 +6111,10 @@
         <v/>
       </c>
       <c r="O101" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P101" t="str">
-        <v/>
+        <v>PO lifecycle+Approval; reports API+UI; vendor/PO query APIs</v>
       </c>
     </row>
     <row r="102">
@@ -6152,7 +6152,7 @@
         <v>5</v>
       </c>
       <c r="L102" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M102" t="str">
         <v/>
@@ -6161,10 +6161,10 @@
         <v/>
       </c>
       <c r="O102" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P102" t="str">
-        <v/>
+        <v>PO lifecycle+Approval; reports API+UI; vendor/PO query APIs</v>
       </c>
     </row>
     <row r="103">
@@ -6202,7 +6202,7 @@
         <v>13</v>
       </c>
       <c r="L103" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M103" t="str">
         <v/>
@@ -6211,10 +6211,10 @@
         <v/>
       </c>
       <c r="O103" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P103" t="str">
-        <v/>
+        <v>PO lifecycle+Approval; reports API+UI; vendor/PO query APIs</v>
       </c>
     </row>
     <row r="104">
@@ -6252,7 +6252,7 @@
         <v>8</v>
       </c>
       <c r="L104" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M104" t="str">
         <v/>
@@ -6261,10 +6261,10 @@
         <v/>
       </c>
       <c r="O104" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P104" t="str">
-        <v/>
+        <v>PO lifecycle+Approval; reports API+UI; vendor/PO query APIs</v>
       </c>
     </row>
     <row r="105">
@@ -6302,7 +6302,7 @@
         <v>8</v>
       </c>
       <c r="L105" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M105" t="str">
         <v/>
@@ -6311,10 +6311,10 @@
         <v>US-S17-002</v>
       </c>
       <c r="O105" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P105" t="str">
-        <v/>
+        <v>AR/profitability reports; portal_users auth+read APIs</v>
       </c>
     </row>
     <row r="106">
@@ -6352,7 +6352,7 @@
         <v>13</v>
       </c>
       <c r="L106" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M106" t="str">
         <v/>
@@ -6361,10 +6361,10 @@
         <v>US-S11-002,US-S16-002,US-S20-001</v>
       </c>
       <c r="O106" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P106" t="str">
-        <v/>
+        <v>AR/profitability reports; portal_users auth+read APIs</v>
       </c>
     </row>
     <row r="107">
@@ -6402,7 +6402,7 @@
         <v>5</v>
       </c>
       <c r="L107" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M107" t="str">
         <v/>
@@ -6411,10 +6411,10 @@
         <v/>
       </c>
       <c r="O107" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P107" t="str">
-        <v/>
+        <v>AR/profitability reports; portal_users auth+read APIs</v>
       </c>
     </row>
     <row r="108">
@@ -6452,7 +6452,7 @@
         <v>13</v>
       </c>
       <c r="L108" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M108" t="str">
         <v/>
@@ -6461,10 +6461,10 @@
         <v/>
       </c>
       <c r="O108" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P108" t="str">
-        <v/>
+        <v>AR/profitability reports; portal_users auth+read APIs</v>
       </c>
     </row>
     <row r="109">
@@ -6502,7 +6502,7 @@
         <v>13</v>
       </c>
       <c r="L109" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M109" t="str">
         <v/>
@@ -6511,10 +6511,10 @@
         <v>US-S25-001</v>
       </c>
       <c r="O109" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P109" t="str">
-        <v/>
+        <v>AR/profitability reports; portal_users auth+read APIs</v>
       </c>
     </row>
     <row r="110">
@@ -6552,7 +6552,7 @@
         <v>13</v>
       </c>
       <c r="L110" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M110" t="str">
         <v/>
@@ -6561,7 +6561,7 @@
         <v>US-S25-002</v>
       </c>
       <c r="O110" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P110" t="str">
         <v/>
@@ -6602,7 +6602,7 @@
         <v>8</v>
       </c>
       <c r="L111" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M111" t="str">
         <v/>
@@ -6611,7 +6611,7 @@
         <v/>
       </c>
       <c r="O111" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P111" t="str">
         <v/>
@@ -6652,7 +6652,7 @@
         <v>8</v>
       </c>
       <c r="L112" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M112" t="str">
         <v/>
@@ -6661,7 +6661,7 @@
         <v/>
       </c>
       <c r="O112" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P112" t="str">
         <v/>
@@ -6702,7 +6702,7 @@
         <v>5</v>
       </c>
       <c r="L113" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M113" t="str">
         <v/>
@@ -6711,7 +6711,7 @@
         <v/>
       </c>
       <c r="O113" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P113" t="str">
         <v/>
@@ -6752,7 +6752,7 @@
         <v>8</v>
       </c>
       <c r="L114" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M114" t="str">
         <v/>
@@ -6761,7 +6761,7 @@
         <v/>
       </c>
       <c r="O114" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P114" t="str">
         <v/>
@@ -6852,7 +6852,7 @@
         <v>5</v>
       </c>
       <c r="L116" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M116" t="str">
         <v/>
@@ -6861,7 +6861,7 @@
         <v/>
       </c>
       <c r="O116" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P116" t="str">
         <v/>
@@ -6902,7 +6902,7 @@
         <v>5</v>
       </c>
       <c r="L117" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M117" t="str">
         <v/>
@@ -6911,7 +6911,7 @@
         <v/>
       </c>
       <c r="O117" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P117" t="str">
         <v/>
@@ -6952,7 +6952,7 @@
         <v>5</v>
       </c>
       <c r="L118" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M118" t="str">
         <v/>
@@ -6961,7 +6961,7 @@
         <v/>
       </c>
       <c r="O118" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P118" t="str">
         <v/>
@@ -7002,7 +7002,7 @@
         <v>5</v>
       </c>
       <c r="L119" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M119" t="str">
         <v/>
@@ -7011,7 +7011,7 @@
         <v/>
       </c>
       <c r="O119" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P119" t="str">
         <v/>
@@ -7052,7 +7052,7 @@
         <v>5</v>
       </c>
       <c r="L120" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M120" t="str">
         <v/>
@@ -7061,7 +7061,7 @@
         <v/>
       </c>
       <c r="O120" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P120" t="str">
         <v/>
@@ -7152,7 +7152,7 @@
         <v>5</v>
       </c>
       <c r="L122" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M122" t="str">
         <v/>
@@ -7161,7 +7161,7 @@
         <v/>
       </c>
       <c r="O122" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P122" t="str">
         <v/>
@@ -7202,7 +7202,7 @@
         <v>8</v>
       </c>
       <c r="L123" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M123" t="str">
         <v/>
@@ -7211,7 +7211,7 @@
         <v>US-S15-001</v>
       </c>
       <c r="O123" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P123" t="str">
         <v/>
@@ -7252,7 +7252,7 @@
         <v>3</v>
       </c>
       <c r="L124" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M124" t="str">
         <v/>
@@ -7261,7 +7261,7 @@
         <v/>
       </c>
       <c r="O124" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P124" t="str">
         <v/>
@@ -7302,7 +7302,7 @@
         <v>8</v>
       </c>
       <c r="L125" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M125" t="str">
         <v/>
@@ -7311,7 +7311,7 @@
         <v>US-S11-002</v>
       </c>
       <c r="O125" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P125" t="str">
         <v/>
@@ -7352,7 +7352,7 @@
         <v>8</v>
       </c>
       <c r="L126" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M126" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>US-S20-001,US-S21-002</v>
       </c>
       <c r="O126" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P126" t="str">
         <v/>
@@ -7402,7 +7402,7 @@
         <v>5</v>
       </c>
       <c r="L127" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M127" t="str">
         <v/>
@@ -7411,7 +7411,7 @@
         <v>US-S3-001</v>
       </c>
       <c r="O127" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P127" t="str">
         <v/>
@@ -7452,7 +7452,7 @@
         <v>5</v>
       </c>
       <c r="L128" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M128" t="str">
         <v/>
@@ -7461,7 +7461,7 @@
         <v/>
       </c>
       <c r="O128" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P128" t="str">
         <v/>
@@ -7502,7 +7502,7 @@
         <v>13</v>
       </c>
       <c r="L129" t="str">
-        <v>Not Started</v>
+        <v>Done</v>
       </c>
       <c r="M129" t="str">
         <v/>
@@ -7511,7 +7511,7 @@
         <v/>
       </c>
       <c r="O129" t="str">
-        <v/>
+        <v>2026-09-24</v>
       </c>
       <c r="P129" t="str">
         <v/>
